--- a/esyluban/examples/dev/DataTables/bonus/掉落表.xlsx
+++ b/esyluban/examples/dev/DataTables/bonus/掉落表.xlsx
@@ -1462,7 +1462,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E1:CD1"/>
+    <mergeCell ref="E2:CD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1491,6 +1491,11 @@
           <t>##export=false</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>常用奖励类型及格式备注说明</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
